--- a/stacked_model/results/baseline/baseline_comparison_summary.xlsx
+++ b/stacked_model/results/baseline/baseline_comparison_summary.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>90.85719869579637</v>
+        <v>90.85719869579707</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>90.33897607891215</v>
+        <v>90.26621989035854</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.372071372961212</v>
+        <v>8.372071372960381</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.359699350431534</v>
+        <v>6.339640638339641</v>
       </c>
     </row>
     <row r="7">
